--- a/Datas/Spawn.xlsx
+++ b/Datas/Spawn.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>示例</t>
-  </si>
-  <si>
-    <t>Small:6|Medium:15|Large:20|Special:15</t>
   </si>
 </sst>
 </file>
@@ -1064,8 +1061,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="4" width="48.625" customWidth="1"/>
@@ -1158,18 +1155,10 @@
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="4"/>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5">
       <c r="A7" s="4"/>
@@ -1178,14 +1167,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" ht="28" customHeight="1"/>
+    <row r="8" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/Spawn.xlsx
+++ b/Datas/Spawn.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/Spawn.xlsx
+++ b/Datas/Spawn.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>Small:0.25|Medium:0.35|Large:0.3|Special:0.1</t>
+    <t>Small:25|Medium:35|Large:30|Special:10</t>
   </si>
   <si>
     <t>Small:8|Medium:12|Large:15|Special:10</t>

--- a/Datas/Spawn.xlsx
+++ b/Datas/Spawn.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,10 @@
     <t>备注</t>
   </si>
   <si>
-    <t>Small:25|Medium:35|Large:30|Special:10</t>
-  </si>
-  <si>
-    <t>Small:8|Medium:12|Large:15|Special:10</t>
+    <t>Small:40|Medium:45|Large:10|Special:5</t>
+  </si>
+  <si>
+    <t>Small:10|Medium:16|Large:30|Special:30</t>
   </si>
   <si>
     <t>示例</t>

--- a/Datas/Spawn.xlsx
+++ b/Datas/Spawn.xlsx
@@ -82,7 +82,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>Small:40|Medium:45|Large:10|Special:5</t>
+    <t>Small:50|Medium:30|Large:10|Special:10</t>
   </si>
   <si>
     <t>Small:10|Medium:16|Large:30|Special:30</t>
